--- a/UN Voting Alignment/china_alignment_graph_data_with_intervals.xlsx
+++ b/UN Voting Alignment/china_alignment_graph_data_with_intervals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofstandrews907-my.sharepoint.com/personal/sk310_st-andrews_ac_uk/Documents/Desktop/IR Dissertation/Python_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofstandrews907-my.sharepoint.com/personal/sk310_st-andrews_ac_uk/Documents/Desktop/IR Dissertation/Upload to git/China-Iran-Relations-Dataset/UN Voting Alignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="71" documentId="11_6AC61CC7B8B06EB29F827612E2FFEC74BC897FFF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88808BA5-D791-4C01-B005-4BA37EB81845}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1455" yWindow="4095" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All_Y_Raw Agreement %" sheetId="1" r:id="rId1"/>
@@ -30,65 +30,6 @@
     <sheet name="ME_5Y_Cohen's Kappa" sheetId="15" r:id="rId15"/>
     <sheet name="ME_5Y_S-Score" sheetId="16" r:id="rId16"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'All_Y_Cohen''s Kappa'!$A$2:$A$55</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'All_Y_Cohen''s Kappa'!$B$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'All_Y_Cohen''s Kappa'!$F$2:$F$55</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'All_Y_Cohen''s Kappa'!$G$1</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'All_Y_Cohen''s Kappa'!$G$2:$G$55</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'All_Y_Cohen''s Kappa'!$H$1</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'All_Y_Cohen''s Kappa'!$H$2:$H$55</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'All_Y_Cohen''s Kappa'!$I$1</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'All_Y_Cohen''s Kappa'!$I$2:$I$55</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'All_Y_Cohen''s Kappa'!$J$1</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'All_Y_Cohen''s Kappa'!$J$2:$J$55</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'All_Y_Cohen''s Kappa'!$A$2:$A$55</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'All_Y_Cohen''s Kappa'!$B$2:$B$55</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'All_Y_Cohen''s Kappa'!$B$1</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'All_Y_Cohen''s Kappa'!$B$2:$B$55</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'All_Y_Cohen''s Kappa'!$C$1</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'All_Y_Cohen''s Kappa'!$C$2:$C$55</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'All_Y_Cohen''s Kappa'!$D$1</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'All_Y_Cohen''s Kappa'!$D$2:$D$55</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'All_Y_Cohen''s Kappa'!$E$1</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'All_Y_Cohen''s Kappa'!$E$2:$E$55</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'All_Y_Cohen''s Kappa'!$F$1</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'All_Y_Cohen''s Kappa'!$F$2:$F$55</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'All_Y_Cohen''s Kappa'!$C$1</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'All_Y_Cohen''s Kappa'!$G$1</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'All_Y_Cohen''s Kappa'!$G$2:$G$55</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'All_Y_Cohen''s Kappa'!$H$1</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'All_Y_Cohen''s Kappa'!$H$2:$H$55</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'All_Y_Cohen''s Kappa'!$I$1</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'All_Y_Cohen''s Kappa'!$I$2:$I$55</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'All_Y_Cohen''s Kappa'!$J$1</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'All_Y_Cohen''s Kappa'!$J$2:$J$55</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'All_Y_Cohen''s Kappa'!$A$2:$A$55</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'All_Y_Cohen''s Kappa'!$B$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'All_Y_Cohen''s Kappa'!$C$2:$C$55</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">'All_Y_Cohen''s Kappa'!$B$2:$B$55</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">'All_Y_Cohen''s Kappa'!$C$1</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">'All_Y_Cohen''s Kappa'!$C$2:$C$55</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">'All_Y_Cohen''s Kappa'!$D$1</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">'All_Y_Cohen''s Kappa'!$D$2:$D$55</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">'All_Y_Cohen''s Kappa'!$E$1</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">'All_Y_Cohen''s Kappa'!$E$2:$E$55</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">'All_Y_Cohen''s Kappa'!$F$1</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">'All_Y_Cohen''s Kappa'!$F$2:$F$55</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">'All_Y_Cohen''s Kappa'!$G$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'All_Y_Cohen''s Kappa'!$D$1</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">'All_Y_Cohen''s Kappa'!$G$2:$G$55</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">'All_Y_Cohen''s Kappa'!$H$1</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">'All_Y_Cohen''s Kappa'!$H$2:$H$55</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">'All_Y_Cohen''s Kappa'!$I$1</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">'All_Y_Cohen''s Kappa'!$I$2:$I$55</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">'All_Y_Cohen''s Kappa'!$J$1</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">'All_Y_Cohen''s Kappa'!$J$2:$J$55</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'All_Y_Cohen''s Kappa'!$D$2:$D$55</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'All_Y_Cohen''s Kappa'!$E$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'All_Y_Cohen''s Kappa'!$E$2:$E$55</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'All_Y_Cohen''s Kappa'!$F$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -323,7 +264,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7825,7 +7766,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -11576,7 +11517,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -17284,7 +17225,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$F$1</c15:sqref>
@@ -17325,7 +17266,7 @@
                 </c:marker>
                 <c:cat>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$A$2:$A$55</c15:sqref>
@@ -17502,7 +17443,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$F$2:$F$55</c15:sqref>
@@ -17678,7 +17619,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-0DC2-4CB2-9FED-82E7DE4B2B83}"/>
                   </c:ext>
@@ -17691,7 +17632,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$G$1</c15:sqref>
@@ -17732,7 +17673,7 @@
                 </c:marker>
                 <c:cat>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$A$2:$A$55</c15:sqref>
@@ -17909,7 +17850,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$G$2:$G$55</c15:sqref>
@@ -18085,7 +18026,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000005-0DC2-4CB2-9FED-82E7DE4B2B83}"/>
                   </c:ext>
@@ -18098,7 +18039,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$H$1</c15:sqref>
@@ -18145,7 +18086,7 @@
                 </c:marker>
                 <c:cat>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$A$2:$A$55</c15:sqref>
@@ -18322,7 +18263,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$H$2:$H$55</c15:sqref>
@@ -18498,7 +18439,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-0DC2-4CB2-9FED-82E7DE4B2B83}"/>
                   </c:ext>
@@ -18511,7 +18452,7 @@
                 <c:order val="8"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$J$1</c15:sqref>
@@ -18558,7 +18499,7 @@
                 </c:marker>
                 <c:cat>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$A$2:$A$55</c15:sqref>
@@ -18735,7 +18676,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'All_Y_Cohen''s Kappa'!$J$2:$J$55</c15:sqref>
@@ -18911,7 +18852,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000008-0DC2-4CB2-9FED-82E7DE4B2B83}"/>
                   </c:ext>
@@ -20617,7 +20558,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -24368,7 +24309,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
